--- a/勤怠/勤怠_テスト三郎.xlsx
+++ b/勤怠/勤怠_テスト三郎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\勤怠\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F25E5B-D91E-462E-B54E-B95A3E371CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EFEF21-1CF8-4712-BC9B-D2D583B94A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7410" yWindow="7410" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7545" yWindow="3360" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/勤怠/勤怠_テスト三郎.xlsx
+++ b/勤怠/勤怠_テスト三郎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\勤怠\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EFEF21-1CF8-4712-BC9B-D2D583B94A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84981A2-6F68-4D1F-8A41-FBA04A74D6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7545" yWindow="3360" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
